--- a/STARTS/START40.xlsx
+++ b/STARTS/START40.xlsx
@@ -461,7 +461,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D56"/>
+  <dimension ref="A1:G56"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="28" customHeight="1"/>
   <cols>
     <col width="65.1640625" customWidth="1" style="2" min="1" max="1"/>
@@ -478,261 +478,551 @@
           <t>Title</t>
         </is>
       </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>used</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>used_at</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>used_project</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="28" customHeight="1">
       <c r="A2" s="3" t="n"/>
       <c r="B2" s="3" t="n"/>
       <c r="C2" s="3" t="n"/>
       <c r="D2" s="3" t="n"/>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
     </row>
     <row r="3" ht="28" customHeight="1">
       <c r="A3" s="3" t="n"/>
       <c r="B3" s="3" t="n"/>
       <c r="C3" s="3" t="n"/>
       <c r="D3" s="3" t="n"/>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="3" t="n"/>
       <c r="B4" s="3" t="n"/>
       <c r="C4" s="3" t="n"/>
       <c r="D4" s="3" t="n"/>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
     </row>
     <row r="5" ht="28" customHeight="1">
       <c r="A5" s="4" t="n"/>
       <c r="B5" s="3" t="n"/>
       <c r="C5" s="3" t="n"/>
       <c r="D5" s="3" t="n"/>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="3" t="n"/>
       <c r="B6" s="3" t="n"/>
       <c r="C6" s="3" t="n"/>
       <c r="D6" s="3" t="n"/>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="3" t="n"/>
       <c r="B7" s="3" t="n"/>
       <c r="C7" s="3" t="n"/>
       <c r="D7" s="3" t="n"/>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
     </row>
     <row r="8" ht="28" customHeight="1">
       <c r="A8" s="3" t="n"/>
       <c r="B8" s="3" t="n"/>
       <c r="C8" s="3" t="n"/>
       <c r="D8" s="3" t="n"/>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
     </row>
     <row r="9" ht="28" customHeight="1">
       <c r="A9" s="3" t="n"/>
       <c r="B9" s="3" t="n"/>
       <c r="C9" s="3" t="n"/>
       <c r="D9" s="3" t="n"/>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="3" t="n"/>
       <c r="B10" s="3" t="n"/>
       <c r="C10" s="3" t="n"/>
       <c r="D10" s="3" t="n"/>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
     </row>
     <row r="11" ht="28" customHeight="1">
       <c r="A11" s="3" t="n"/>
       <c r="B11" s="3" t="n"/>
       <c r="C11" s="3" t="n"/>
       <c r="D11" s="3" t="n"/>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
     </row>
     <row r="12" ht="28" customHeight="1">
       <c r="A12" s="3" t="n"/>
       <c r="B12" s="3" t="n"/>
       <c r="C12" s="3" t="n"/>
       <c r="D12" s="3" t="n"/>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
     </row>
     <row r="13" ht="28" customHeight="1">
       <c r="A13" s="3" t="n"/>
       <c r="B13" s="3" t="n"/>
       <c r="C13" s="3" t="n"/>
       <c r="D13" s="3" t="n"/>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
     </row>
     <row r="14" ht="28" customHeight="1">
       <c r="A14" s="3" t="n"/>
       <c r="B14" s="3" t="n"/>
       <c r="C14" s="3" t="n"/>
       <c r="D14" s="3" t="n"/>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
     </row>
     <row r="15" ht="28" customHeight="1">
       <c r="A15" s="3" t="n"/>
       <c r="B15" s="3" t="n"/>
       <c r="C15" s="3" t="n"/>
       <c r="D15" s="3" t="n"/>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
     </row>
     <row r="16" ht="28" customHeight="1">
       <c r="A16" s="3" t="n"/>
       <c r="B16" s="3" t="n"/>
       <c r="C16" s="3" t="n"/>
       <c r="D16" s="3" t="n"/>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
     </row>
     <row r="17" ht="28" customHeight="1">
       <c r="A17" s="3" t="n"/>
       <c r="B17" s="3" t="n"/>
       <c r="C17" s="3" t="n"/>
       <c r="D17" s="3" t="n"/>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
     </row>
     <row r="18" ht="28" customHeight="1">
       <c r="A18" s="3" t="n"/>
       <c r="B18" s="3" t="n"/>
       <c r="C18" s="3" t="n"/>
       <c r="D18" s="3" t="n"/>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
     </row>
     <row r="19" ht="28" customHeight="1">
       <c r="A19" s="3" t="n"/>
       <c r="B19" s="3" t="n"/>
       <c r="C19" s="3" t="n"/>
       <c r="D19" s="3" t="n"/>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
     </row>
     <row r="20" ht="28" customHeight="1">
       <c r="A20" s="3" t="n"/>
       <c r="B20" s="3" t="n"/>
       <c r="C20" s="3" t="n"/>
       <c r="D20" s="3" t="n"/>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
     </row>
     <row r="21" ht="28" customHeight="1">
       <c r="A21" s="3" t="n"/>
       <c r="B21" s="3" t="n"/>
       <c r="C21" s="3" t="n"/>
       <c r="D21" s="3" t="n"/>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
     </row>
     <row r="22" ht="28" customHeight="1">
       <c r="A22" s="3" t="n"/>
       <c r="B22" s="3" t="n"/>
       <c r="C22" s="3" t="n"/>
       <c r="D22" s="3" t="n"/>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
     </row>
     <row r="23" ht="28" customHeight="1">
       <c r="A23" s="3" t="n"/>
       <c r="B23" s="3" t="n"/>
       <c r="C23" s="3" t="n"/>
       <c r="D23" s="3" t="n"/>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
     </row>
     <row r="24" ht="28" customHeight="1">
       <c r="A24" s="3" t="n"/>
       <c r="B24" s="3" t="n"/>
       <c r="C24" s="3" t="n"/>
       <c r="D24" s="3" t="n"/>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
     </row>
     <row r="25" ht="28" customHeight="1">
       <c r="A25" s="3" t="n"/>
       <c r="B25" s="3" t="n"/>
       <c r="C25" s="3" t="n"/>
       <c r="D25" s="3" t="n"/>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
     </row>
     <row r="26" ht="28" customHeight="1">
       <c r="A26" s="3" t="n"/>
       <c r="B26" s="3" t="n"/>
       <c r="C26" s="3" t="n"/>
       <c r="D26" s="3" t="n"/>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
     </row>
     <row r="27" ht="28" customHeight="1">
       <c r="A27" s="3" t="n"/>
       <c r="B27" s="3" t="n"/>
       <c r="C27" s="3" t="n"/>
       <c r="D27" s="3" t="n"/>
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
     </row>
     <row r="28" ht="28" customHeight="1">
       <c r="A28" s="3" t="n"/>
       <c r="B28" s="3" t="n"/>
       <c r="C28" s="3" t="n"/>
       <c r="D28" s="3" t="n"/>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
     </row>
     <row r="29" ht="28" customHeight="1">
       <c r="A29" s="3" t="n"/>
       <c r="B29" s="3" t="n"/>
       <c r="C29" s="3" t="n"/>
       <c r="D29" s="3" t="n"/>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
     </row>
     <row r="30" ht="28" customHeight="1">
       <c r="A30" s="3" t="n"/>
       <c r="B30" s="3" t="n"/>
       <c r="C30" s="3" t="n"/>
       <c r="D30" s="3" t="n"/>
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
     </row>
     <row r="31" ht="28" customHeight="1">
       <c r="A31" s="3" t="n"/>
       <c r="B31" s="3" t="n"/>
       <c r="C31" s="3" t="n"/>
       <c r="D31" s="3" t="n"/>
+      <c r="E31" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
     </row>
     <row r="32" ht="28" customHeight="1">
       <c r="A32" s="3" t="n"/>
+      <c r="E32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
     </row>
     <row r="33" ht="28" customHeight="1">
       <c r="A33" s="3" t="n"/>
+      <c r="E33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
     </row>
     <row r="34" ht="28" customHeight="1">
       <c r="A34" s="3" t="n"/>
+      <c r="E34" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
     </row>
     <row r="35" ht="28" customHeight="1">
       <c r="A35" s="3" t="n"/>
+      <c r="E35" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
     </row>
     <row r="36" ht="28" customHeight="1">
       <c r="A36" s="3" t="n"/>
+      <c r="E36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
     </row>
     <row r="37" ht="28" customHeight="1">
       <c r="A37" s="3" t="n"/>
+      <c r="E37" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
     </row>
     <row r="38" ht="28" customHeight="1">
       <c r="A38" s="3" t="n"/>
+      <c r="E38" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr"/>
     </row>
     <row r="39" ht="28" customHeight="1">
       <c r="A39" s="3" t="n"/>
+      <c r="E39" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr"/>
     </row>
     <row r="40" ht="28" customHeight="1">
       <c r="A40" s="3" t="n"/>
+      <c r="E40" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr"/>
     </row>
     <row r="41" ht="28" customHeight="1">
       <c r="A41" s="3" t="n"/>
+      <c r="E41" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
     </row>
     <row r="42" ht="28" customHeight="1">
       <c r="A42" s="3" t="n"/>
+      <c r="E42" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
     </row>
     <row r="43" ht="28" customHeight="1">
       <c r="A43" s="3" t="n"/>
+      <c r="E43" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr"/>
     </row>
     <row r="44" ht="28" customHeight="1">
       <c r="A44" s="3" t="n"/>
+      <c r="E44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr"/>
     </row>
     <row r="45" ht="28" customHeight="1">
       <c r="A45" s="3" t="n"/>
+      <c r="E45" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr"/>
     </row>
     <row r="46" ht="28" customHeight="1">
       <c r="A46" s="3" t="n"/>
+      <c r="E46" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr"/>
     </row>
     <row r="47" ht="28" customHeight="1">
       <c r="A47" s="3" t="n"/>
+      <c r="E47" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr"/>
     </row>
     <row r="48" ht="28" customHeight="1">
       <c r="A48" s="3" t="n"/>
+      <c r="E48" t="n">
+        <v>0</v>
+      </c>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr"/>
     </row>
     <row r="49" ht="28" customHeight="1">
       <c r="A49" s="3" t="n"/>
+      <c r="E49" t="n">
+        <v>0</v>
+      </c>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr"/>
     </row>
     <row r="50" ht="28" customHeight="1">
       <c r="A50" s="3" t="n"/>
+      <c r="E50" t="n">
+        <v>0</v>
+      </c>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr"/>
     </row>
     <row r="51" ht="28" customHeight="1">
       <c r="A51" s="3" t="n"/>
+      <c r="E51" t="n">
+        <v>0</v>
+      </c>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr"/>
     </row>
     <row r="52" ht="28" customHeight="1">
       <c r="A52" s="3" t="n"/>
+      <c r="E52" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr"/>
     </row>
     <row r="53" ht="28" customHeight="1">
       <c r="A53" s="3" t="n"/>
+      <c r="E53" t="n">
+        <v>0</v>
+      </c>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr"/>
     </row>
     <row r="54" ht="28" customHeight="1">
       <c r="A54" s="3" t="n"/>
+      <c r="E54" t="n">
+        <v>0</v>
+      </c>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr"/>
     </row>
     <row r="55" ht="28" customHeight="1">
       <c r="A55" s="3" t="n"/>
+      <c r="E55" t="n">
+        <v>0</v>
+      </c>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr"/>
     </row>
     <row r="56" ht="28" customHeight="1">
       <c r="A56" s="3" t="n"/>
+      <c r="E56" t="n">
+        <v>0</v>
+      </c>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
